--- a/0.2/docs/BOM_PET_PCB1_2026-05-22.xlsx
+++ b/0.2/docs/BOM_PET_PCB1_2026-05-22.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD5BF74-64DE-4E06-A6CE-A2C1021F7321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="BOM_PET_PCB1_2026-05-22" state="visible" r:id="rId4"/>
+    <sheet name="BOM_PET_PCB1_2026-05-23" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="266">
   <si>
     <t>No.</t>
   </si>
@@ -25,9 +29,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>Footprint</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -169,7 +170,7 @@
     <t>352</t>
   </si>
   <si>
-    <t>0.1736</t>
+    <t>0.1737</t>
   </si>
   <si>
     <t>gge56,gge57</t>
@@ -262,7 +263,7 @@
     <t>C369104</t>
   </si>
   <si>
-    <t>26436</t>
+    <t>26416</t>
   </si>
   <si>
     <t>0.0088</t>
@@ -298,10 +299,10 @@
     <t>Fuseholders</t>
   </si>
   <si>
-    <t>4113</t>
-  </si>
-  <si>
-    <t>0.2122</t>
+    <t>4083</t>
+  </si>
+  <si>
+    <t>0.2123</t>
   </si>
   <si>
     <t>FUSE-TH_4P-L16.0-W6.7-P3.40</t>
@@ -334,7 +335,7 @@
     <t>Pin Headers</t>
   </si>
   <si>
-    <t>364117</t>
+    <t>363457</t>
   </si>
   <si>
     <t>0.0034</t>
@@ -364,7 +365,7 @@
     <t>C124378</t>
   </si>
   <si>
-    <t>92125</t>
+    <t>89958</t>
   </si>
   <si>
     <t>0.0081</t>
@@ -421,7 +422,7 @@
     <t>C50950</t>
   </si>
   <si>
-    <t>170116</t>
+    <t>169377</t>
   </si>
   <si>
     <t>0.0119</t>
@@ -445,7 +446,7 @@
     <t>C2718488</t>
   </si>
   <si>
-    <t>223711</t>
+    <t>223182</t>
   </si>
   <si>
     <t>0.0115</t>
@@ -502,7 +503,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>3228</t>
+    <t>3203</t>
   </si>
   <si>
     <t>0.0156</t>
@@ -550,7 +551,7 @@
     <t>C27438</t>
   </si>
   <si>
-    <t>152234</t>
+    <t>150164</t>
   </si>
   <si>
     <t>0.0157</t>
@@ -580,7 +581,7 @@
     <t>MOSFETs</t>
   </si>
   <si>
-    <t>0.4328</t>
+    <t>0.433</t>
   </si>
   <si>
     <t>gge48,gge49</t>
@@ -613,7 +614,7 @@
     <t>Potentiometers, Variable Resistors</t>
   </si>
   <si>
-    <t>0.2885</t>
+    <t>0.2886</t>
   </si>
   <si>
     <t>gge35</t>
@@ -697,7 +698,7 @@
     <t>C119339</t>
   </si>
   <si>
-    <t>50674</t>
+    <t>50304</t>
   </si>
   <si>
     <t>0.0017</t>
@@ -712,6 +713,18 @@
     <t>21</t>
   </si>
   <si>
+    <t>Screw-Hole-M3</t>
+  </si>
+  <si>
+    <t>SCREW1,SCREW2,SCREW3,SCREW4</t>
+  </si>
+  <si>
+    <t>5425.2902</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>ST-0-103-C03-N003-RS</t>
   </si>
   <si>
@@ -733,16 +746,16 @@
     <t>Toggle Switches</t>
   </si>
   <si>
-    <t>1208</t>
-  </si>
-  <si>
-    <t>0.1187</t>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>0.1188</t>
   </si>
   <si>
     <t>gge59</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>KF301-5.0-3P</t>
@@ -763,7 +776,7 @@
     <t>Screw Terminal Blocks</t>
   </si>
   <si>
-    <t>23836</t>
+    <t>23721</t>
   </si>
   <si>
     <t>0.0186</t>
@@ -772,7 +785,7 @@
     <t>gge42</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>10Ω</t>
@@ -797,19 +810,22 @@
   </si>
   <si>
     <t>gge46,gge46_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1172,14 +1188,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z25"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="26" width="20" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1193,1920 +1224,2000 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>26</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>35</v>
       </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
       <c r="N2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
         <v>37</v>
       </c>
-      <c r="O2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>39</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>41</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>43</v>
-      </c>
       <c r="Z2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
         <v>44</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
         <v>46</v>
       </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>47</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>48</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
         <v>49</v>
       </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
         <v>50</v>
       </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>46</v>
+      </c>
+      <c r="X3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y3" t="s">
         <v>52</v>
       </c>
-      <c r="R3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" t="s">
-        <v>42</v>
-      </c>
-      <c r="U3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" t="s">
-        <v>46</v>
-      </c>
-      <c r="W3" t="s">
-        <v>47</v>
-      </c>
-      <c r="X3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>53</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>54</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>56</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>58</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
         <v>59</v>
       </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>60</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
         <v>61</v>
       </c>
-      <c r="M4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y4" t="s">
         <v>63</v>
       </c>
-      <c r="R4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" t="s">
-        <v>42</v>
-      </c>
-      <c r="U4" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W4" t="s">
-        <v>55</v>
-      </c>
-      <c r="X4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>64</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
         <v>66</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>67</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" t="s">
         <v>68</v>
       </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>69</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
         <v>70</v>
       </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>71</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" t="s">
         <v>72</v>
       </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" t="s">
         <v>74</v>
       </c>
-      <c r="R5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y5" t="s">
         <v>75</v>
       </c>
-      <c r="W5" t="s">
-        <v>66</v>
-      </c>
-      <c r="X5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>76</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>77</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
         <v>78</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>79</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" t="s">
         <v>80</v>
       </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>81</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" t="s">
         <v>82</v>
       </c>
-      <c r="J6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>83</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" t="s">
+        <v>40</v>
+      </c>
+      <c r="T6" t="s">
+        <v>41</v>
+      </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" t="s">
         <v>84</v>
       </c>
-      <c r="R6" t="s">
-        <v>40</v>
-      </c>
-      <c r="S6" t="s">
-        <v>41</v>
-      </c>
-      <c r="T6" t="s">
-        <v>42</v>
-      </c>
-      <c r="U6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>85</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y6" t="s">
         <v>86</v>
       </c>
-      <c r="X6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>87</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>88</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
         <v>89</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>90</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
         <v>91</v>
       </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>92</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" t="s">
         <v>93</v>
       </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" t="s">
         <v>94</v>
       </c>
-      <c r="M7" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>95</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U7" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" t="s">
         <v>96</v>
       </c>
-      <c r="R7" t="s">
-        <v>40</v>
-      </c>
-      <c r="S7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" t="s">
-        <v>42</v>
-      </c>
-      <c r="U7" t="s">
-        <v>37</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y7" t="s">
         <v>97</v>
       </c>
-      <c r="W7" t="s">
-        <v>89</v>
-      </c>
-      <c r="X7" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>98</v>
       </c>
-      <c r="Z7" t="s">
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>100</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
         <v>101</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>102</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" t="s">
         <v>103</v>
       </c>
-      <c r="F8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>104</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s">
         <v>105</v>
       </c>
-      <c r="J8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" t="s">
         <v>106</v>
       </c>
-      <c r="M8" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" t="s">
-        <v>37</v>
-      </c>
-      <c r="O8" t="s">
-        <v>37</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>107</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" t="s">
+        <v>40</v>
+      </c>
+      <c r="T8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" t="s">
         <v>108</v>
       </c>
-      <c r="R8" t="s">
-        <v>40</v>
-      </c>
-      <c r="S8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T8" t="s">
-        <v>42</v>
-      </c>
-      <c r="U8" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
+        <v>100</v>
+      </c>
+      <c r="X8" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y8" t="s">
         <v>109</v>
       </c>
-      <c r="W8" t="s">
-        <v>101</v>
-      </c>
-      <c r="X8" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>110</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>111</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
         <v>112</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>113</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" t="s">
         <v>114</v>
       </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>115</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" t="s">
+        <v>105</v>
+      </c>
+      <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" t="s">
         <v>116</v>
       </c>
-      <c r="J9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" t="s">
-        <v>106</v>
-      </c>
-      <c r="M9" t="s">
-        <v>65</v>
-      </c>
-      <c r="N9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>117</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" t="s">
         <v>118</v>
       </c>
-      <c r="R9" t="s">
-        <v>40</v>
-      </c>
-      <c r="S9" t="s">
-        <v>41</v>
-      </c>
-      <c r="T9" t="s">
-        <v>42</v>
-      </c>
-      <c r="U9" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
+        <v>111</v>
+      </c>
+      <c r="X9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y9" t="s">
         <v>119</v>
       </c>
-      <c r="W9" t="s">
-        <v>112</v>
-      </c>
-      <c r="X9" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y9" t="s">
+      <c r="Z9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>120</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>121</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
         <v>122</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>123</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" t="s">
         <v>124</v>
       </c>
-      <c r="F10" t="s">
+      <c r="I10" t="s">
+        <v>125</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" t="s">
         <v>37</v>
       </c>
-      <c r="G10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="Q10" t="s">
         <v>127</v>
       </c>
-      <c r="M10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N10" t="s">
-        <v>37</v>
-      </c>
-      <c r="O10" t="s">
-        <v>37</v>
-      </c>
-      <c r="P10" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" t="s">
+        <v>40</v>
+      </c>
+      <c r="T10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U10" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" t="s">
         <v>128</v>
       </c>
-      <c r="R10" t="s">
-        <v>40</v>
-      </c>
-      <c r="S10" t="s">
-        <v>41</v>
-      </c>
-      <c r="T10" t="s">
-        <v>42</v>
-      </c>
-      <c r="U10" t="s">
-        <v>37</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
+        <v>121</v>
+      </c>
+      <c r="X10" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y10" t="s">
         <v>129</v>
       </c>
-      <c r="W10" t="s">
-        <v>122</v>
-      </c>
-      <c r="X10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="Z10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>130</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>131</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" t="s">
         <v>132</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>133</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" t="s">
         <v>134</v>
       </c>
-      <c r="F11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" t="s">
         <v>135</v>
       </c>
-      <c r="J11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" t="s">
-        <v>127</v>
-      </c>
-      <c r="M11" t="s">
-        <v>77</v>
-      </c>
-      <c r="N11" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" t="s">
-        <v>37</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>136</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" t="s">
+        <v>40</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" t="s">
+        <v>133</v>
+      </c>
+      <c r="W11" t="s">
+        <v>131</v>
+      </c>
+      <c r="X11" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y11" t="s">
         <v>137</v>
       </c>
-      <c r="R11" t="s">
-        <v>40</v>
-      </c>
-      <c r="S11" t="s">
-        <v>41</v>
-      </c>
-      <c r="T11" t="s">
-        <v>42</v>
-      </c>
-      <c r="U11" t="s">
-        <v>37</v>
-      </c>
-      <c r="V11" t="s">
-        <v>134</v>
-      </c>
-      <c r="W11" t="s">
-        <v>132</v>
-      </c>
-      <c r="X11" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y11" t="s">
+      <c r="Z11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>138</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>139</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" t="s">
         <v>140</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>141</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" t="s">
         <v>142</v>
       </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" t="s">
-        <v>140</v>
-      </c>
-      <c r="H12" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" t="s">
+        <v>36</v>
+      </c>
+      <c r="O12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" t="s">
         <v>143</v>
       </c>
-      <c r="J12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" t="s">
-        <v>127</v>
-      </c>
-      <c r="M12" t="s">
-        <v>65</v>
-      </c>
-      <c r="N12" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" t="s">
-        <v>37</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>144</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
+        <v>39</v>
+      </c>
+      <c r="S12" t="s">
+        <v>40</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" t="s">
+        <v>141</v>
+      </c>
+      <c r="W12" t="s">
+        <v>139</v>
+      </c>
+      <c r="X12" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y12" t="s">
         <v>145</v>
       </c>
-      <c r="R12" t="s">
-        <v>40</v>
-      </c>
-      <c r="S12" t="s">
-        <v>41</v>
-      </c>
-      <c r="T12" t="s">
-        <v>42</v>
-      </c>
-      <c r="U12" t="s">
-        <v>37</v>
-      </c>
-      <c r="V12" t="s">
-        <v>142</v>
-      </c>
-      <c r="W12" t="s">
-        <v>140</v>
-      </c>
-      <c r="X12" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y12" t="s">
+      <c r="Z12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>146</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>147</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" t="s">
         <v>148</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>149</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" t="s">
         <v>150</v>
       </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" t="s">
-        <v>148</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
         <v>151</v>
       </c>
-      <c r="J13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>152</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" t="s">
         <v>153</v>
       </c>
-      <c r="M13" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" t="s">
-        <v>37</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>154</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S13" t="s">
+        <v>40</v>
+      </c>
+      <c r="T13" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13" t="s">
+        <v>36</v>
+      </c>
+      <c r="V13" t="s">
+        <v>149</v>
+      </c>
+      <c r="W13" t="s">
+        <v>147</v>
+      </c>
+      <c r="X13" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y13" t="s">
         <v>155</v>
       </c>
-      <c r="R13" t="s">
-        <v>40</v>
-      </c>
-      <c r="S13" t="s">
-        <v>41</v>
-      </c>
-      <c r="T13" t="s">
-        <v>42</v>
-      </c>
-      <c r="U13" t="s">
-        <v>37</v>
-      </c>
-      <c r="V13" t="s">
-        <v>150</v>
-      </c>
-      <c r="W13" t="s">
-        <v>148</v>
-      </c>
-      <c r="X13" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y13" t="s">
+      <c r="Z13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>156</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>157</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" t="s">
         <v>158</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>159</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>157</v>
+      </c>
+      <c r="H14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" t="s">
         <v>160</v>
       </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>158</v>
-      </c>
-      <c r="H14" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" t="s">
         <v>161</v>
       </c>
-      <c r="J14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" t="s">
-        <v>127</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" t="s">
         <v>162</v>
       </c>
-      <c r="N14" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" t="s">
-        <v>37</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>163</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
+        <v>39</v>
+      </c>
+      <c r="S14" t="s">
+        <v>40</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" t="s">
         <v>164</v>
       </c>
-      <c r="R14" t="s">
-        <v>40</v>
-      </c>
-      <c r="S14" t="s">
-        <v>41</v>
-      </c>
-      <c r="T14" t="s">
-        <v>42</v>
-      </c>
-      <c r="U14" t="s">
-        <v>37</v>
-      </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
+        <v>157</v>
+      </c>
+      <c r="X14" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y14" t="s">
         <v>165</v>
       </c>
-      <c r="W14" t="s">
-        <v>158</v>
-      </c>
-      <c r="X14" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y14" t="s">
+      <c r="Z14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>166</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>167</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" t="s">
         <v>168</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>169</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" t="s">
         <v>170</v>
       </c>
-      <c r="F15" t="s">
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15" t="s">
         <v>37</v>
       </c>
-      <c r="G15" t="s">
-        <v>168</v>
-      </c>
-      <c r="H15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="Q15" t="s">
         <v>171</v>
       </c>
-      <c r="J15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" t="s">
-        <v>37</v>
-      </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" t="s">
-        <v>37</v>
-      </c>
-      <c r="P15" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
+        <v>39</v>
+      </c>
+      <c r="S15" t="s">
+        <v>40</v>
+      </c>
+      <c r="T15" t="s">
+        <v>41</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" t="s">
+        <v>169</v>
+      </c>
+      <c r="W15" t="s">
+        <v>167</v>
+      </c>
+      <c r="X15" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y15" t="s">
         <v>172</v>
       </c>
-      <c r="R15" t="s">
-        <v>40</v>
-      </c>
-      <c r="S15" t="s">
-        <v>41</v>
-      </c>
-      <c r="T15" t="s">
-        <v>42</v>
-      </c>
-      <c r="U15" t="s">
-        <v>37</v>
-      </c>
-      <c r="V15" t="s">
-        <v>170</v>
-      </c>
-      <c r="W15" t="s">
-        <v>168</v>
-      </c>
-      <c r="X15" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y15" t="s">
+      <c r="Z15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>173</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>174</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" t="s">
         <v>175</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>176</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" t="s">
         <v>177</v>
       </c>
-      <c r="F16" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" t="s">
-        <v>175</v>
-      </c>
-      <c r="H16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" t="s">
+        <v>126</v>
+      </c>
+      <c r="M16" t="s">
+        <v>110</v>
+      </c>
+      <c r="N16" t="s">
+        <v>36</v>
+      </c>
+      <c r="O16" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" t="s">
         <v>178</v>
       </c>
-      <c r="J16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" t="s">
-        <v>127</v>
-      </c>
-      <c r="M16" t="s">
-        <v>111</v>
-      </c>
-      <c r="N16" t="s">
-        <v>37</v>
-      </c>
-      <c r="O16" t="s">
-        <v>37</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>179</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S16" t="s">
+        <v>40</v>
+      </c>
+      <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16" t="s">
+        <v>36</v>
+      </c>
+      <c r="V16" t="s">
+        <v>176</v>
+      </c>
+      <c r="W16" t="s">
+        <v>174</v>
+      </c>
+      <c r="X16" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y16" t="s">
         <v>180</v>
       </c>
-      <c r="R16" t="s">
-        <v>40</v>
-      </c>
-      <c r="S16" t="s">
-        <v>41</v>
-      </c>
-      <c r="T16" t="s">
-        <v>42</v>
-      </c>
-      <c r="U16" t="s">
-        <v>37</v>
-      </c>
-      <c r="V16" t="s">
-        <v>177</v>
-      </c>
-      <c r="W16" t="s">
-        <v>175</v>
-      </c>
-      <c r="X16" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>181</v>
-      </c>
       <c r="Z16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" t="s">
         <v>182</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>183</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H17" t="s">
         <v>184</v>
       </c>
-      <c r="F17" t="s">
+      <c r="I17" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" t="s">
         <v>37</v>
       </c>
-      <c r="G17" t="s">
-        <v>182</v>
-      </c>
-      <c r="H17" t="s">
-        <v>185</v>
-      </c>
-      <c r="I17" t="s">
-        <v>186</v>
-      </c>
-      <c r="J17" t="s">
-        <v>33</v>
-      </c>
-      <c r="K17" t="s">
-        <v>187</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="Q17" t="s">
         <v>188</v>
       </c>
-      <c r="M17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" t="s">
-        <v>37</v>
-      </c>
-      <c r="O17" t="s">
-        <v>37</v>
-      </c>
-      <c r="P17" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
+        <v>39</v>
+      </c>
+      <c r="S17" t="s">
+        <v>40</v>
+      </c>
+      <c r="T17" t="s">
+        <v>41</v>
+      </c>
+      <c r="U17" t="s">
+        <v>36</v>
+      </c>
+      <c r="V17" t="s">
+        <v>183</v>
+      </c>
+      <c r="W17" t="s">
+        <v>181</v>
+      </c>
+      <c r="X17" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y17" t="s">
         <v>189</v>
       </c>
-      <c r="R17" t="s">
-        <v>40</v>
-      </c>
-      <c r="S17" t="s">
-        <v>41</v>
-      </c>
-      <c r="T17" t="s">
-        <v>42</v>
-      </c>
-      <c r="U17" t="s">
-        <v>37</v>
-      </c>
-      <c r="V17" t="s">
-        <v>184</v>
-      </c>
-      <c r="W17" t="s">
-        <v>182</v>
-      </c>
-      <c r="X17" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y17" t="s">
+      <c r="Z17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>190</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>191</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" t="s">
         <v>192</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>193</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" t="s">
         <v>194</v>
       </c>
-      <c r="F18" t="s">
-        <v>192</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>195</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>196</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
         <v>197</v>
       </c>
-      <c r="J18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>198</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q18" t="s">
         <v>199</v>
       </c>
-      <c r="M18" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" t="s">
-        <v>37</v>
-      </c>
-      <c r="P18" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18" t="s">
+        <v>40</v>
+      </c>
+      <c r="T18" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" t="s">
+        <v>193</v>
+      </c>
+      <c r="W18" t="s">
+        <v>194</v>
+      </c>
+      <c r="X18" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y18" t="s">
         <v>200</v>
       </c>
-      <c r="R18" t="s">
-        <v>40</v>
-      </c>
-      <c r="S18" t="s">
-        <v>41</v>
-      </c>
-      <c r="T18" t="s">
-        <v>42</v>
-      </c>
-      <c r="U18" t="s">
-        <v>37</v>
-      </c>
-      <c r="V18" t="s">
-        <v>194</v>
-      </c>
-      <c r="W18" t="s">
-        <v>195</v>
-      </c>
-      <c r="X18" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y18" t="s">
+      <c r="Z18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>201</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>202</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" t="s">
         <v>203</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>204</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" t="s">
         <v>205</v>
       </c>
-      <c r="F19" t="s">
-        <v>203</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>206</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>207</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>197</v>
+      </c>
+      <c r="L19" t="s">
         <v>208</v>
       </c>
-      <c r="J19" t="s">
-        <v>33</v>
-      </c>
-      <c r="K19" t="s">
-        <v>198</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
+        <v>35</v>
+      </c>
+      <c r="N19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19" t="s">
         <v>209</v>
       </c>
-      <c r="M19" t="s">
-        <v>36</v>
-      </c>
-      <c r="N19" t="s">
-        <v>37</v>
-      </c>
-      <c r="O19" t="s">
-        <v>37</v>
-      </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>210</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
+        <v>39</v>
+      </c>
+      <c r="S19" t="s">
+        <v>40</v>
+      </c>
+      <c r="T19" t="s">
+        <v>41</v>
+      </c>
+      <c r="U19" t="s">
+        <v>36</v>
+      </c>
+      <c r="V19" t="s">
+        <v>204</v>
+      </c>
+      <c r="W19" t="s">
+        <v>205</v>
+      </c>
+      <c r="X19" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y19" t="s">
         <v>211</v>
       </c>
-      <c r="R19" t="s">
-        <v>40</v>
-      </c>
-      <c r="S19" t="s">
-        <v>41</v>
-      </c>
-      <c r="T19" t="s">
-        <v>42</v>
-      </c>
-      <c r="U19" t="s">
-        <v>37</v>
-      </c>
-      <c r="V19" t="s">
-        <v>205</v>
-      </c>
-      <c r="W19" t="s">
-        <v>206</v>
-      </c>
-      <c r="X19" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y19" t="s">
+      <c r="Z19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>212</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>213</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20" t="s">
         <v>214</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>191</v>
+      </c>
+      <c r="G20" t="s">
         <v>215</v>
       </c>
-      <c r="F20" t="s">
-        <v>192</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>216</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>217</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>197</v>
+      </c>
+      <c r="L20" t="s">
+        <v>208</v>
+      </c>
+      <c r="M20" t="s">
+        <v>35</v>
+      </c>
+      <c r="N20" t="s">
+        <v>36</v>
+      </c>
+      <c r="O20" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20" t="s">
         <v>218</v>
       </c>
-      <c r="J20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" t="s">
-        <v>198</v>
-      </c>
-      <c r="L20" t="s">
-        <v>209</v>
-      </c>
-      <c r="M20" t="s">
-        <v>36</v>
-      </c>
-      <c r="N20" t="s">
-        <v>37</v>
-      </c>
-      <c r="O20" t="s">
-        <v>37</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>219</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
+        <v>39</v>
+      </c>
+      <c r="S20" t="s">
+        <v>40</v>
+      </c>
+      <c r="T20" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" t="s">
+        <v>214</v>
+      </c>
+      <c r="W20" t="s">
+        <v>215</v>
+      </c>
+      <c r="X20" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y20" t="s">
         <v>220</v>
       </c>
-      <c r="R20" t="s">
-        <v>40</v>
-      </c>
-      <c r="S20" t="s">
-        <v>41</v>
-      </c>
-      <c r="T20" t="s">
-        <v>42</v>
-      </c>
-      <c r="U20" t="s">
-        <v>37</v>
-      </c>
-      <c r="V20" t="s">
-        <v>215</v>
-      </c>
-      <c r="W20" t="s">
-        <v>216</v>
-      </c>
-      <c r="X20" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y20" t="s">
+      <c r="Z20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>221</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>222</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
+        <v>222</v>
+      </c>
+      <c r="D21" t="s">
         <v>223</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>224</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" t="s">
         <v>225</v>
       </c>
-      <c r="F21" t="s">
-        <v>223</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
+        <v>206</v>
+      </c>
+      <c r="I21" t="s">
         <v>226</v>
       </c>
-      <c r="H21" t="s">
-        <v>207</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>197</v>
+      </c>
+      <c r="L21" t="s">
+        <v>208</v>
+      </c>
+      <c r="M21" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" t="s">
+        <v>36</v>
+      </c>
+      <c r="O21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21" t="s">
         <v>227</v>
       </c>
-      <c r="J21" t="s">
-        <v>33</v>
-      </c>
-      <c r="K21" t="s">
-        <v>198</v>
-      </c>
-      <c r="L21" t="s">
-        <v>209</v>
-      </c>
-      <c r="M21" t="s">
-        <v>36</v>
-      </c>
-      <c r="N21" t="s">
-        <v>37</v>
-      </c>
-      <c r="O21" t="s">
-        <v>37</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>228</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
+        <v>39</v>
+      </c>
+      <c r="S21" t="s">
+        <v>40</v>
+      </c>
+      <c r="T21" t="s">
+        <v>41</v>
+      </c>
+      <c r="U21" t="s">
+        <v>36</v>
+      </c>
+      <c r="V21" t="s">
         <v>229</v>
       </c>
-      <c r="R21" t="s">
+      <c r="W21" t="s">
+        <v>225</v>
+      </c>
+      <c r="X21" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s">
+        <v>36</v>
+      </c>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>36</v>
+      </c>
+      <c r="O22" t="s">
+        <v>234</v>
+      </c>
+      <c r="P22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" t="s">
+        <v>39</v>
+      </c>
+      <c r="S22" t="s">
         <v>40</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T22" t="s">
         <v>41</v>
       </c>
-      <c r="T21" t="s">
-        <v>42</v>
-      </c>
-      <c r="U21" t="s">
-        <v>37</v>
-      </c>
-      <c r="V21" t="s">
-        <v>230</v>
-      </c>
-      <c r="W21" t="s">
-        <v>226</v>
-      </c>
-      <c r="X21" t="s">
-        <v>223</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>37</v>
+      <c r="U22" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22" t="s">
+        <v>232</v>
+      </c>
+      <c r="X22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>232</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>233</v>
-      </c>
-      <c r="D22" t="s">
-        <v>234</v>
-      </c>
-      <c r="E22" t="s">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>235</v>
-      </c>
-      <c r="F22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" t="s">
-        <v>233</v>
-      </c>
-      <c r="H22" t="s">
-        <v>236</v>
-      </c>
-      <c r="I22" t="s">
-        <v>237</v>
-      </c>
-      <c r="J22" t="s">
-        <v>33</v>
-      </c>
-      <c r="K22" t="s">
-        <v>238</v>
-      </c>
-      <c r="L22" t="s">
-        <v>239</v>
-      </c>
-      <c r="M22" t="s">
-        <v>77</v>
-      </c>
-      <c r="N22" t="s">
-        <v>37</v>
-      </c>
-      <c r="O22" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>241</v>
-      </c>
-      <c r="R22" t="s">
-        <v>40</v>
-      </c>
-      <c r="S22" t="s">
-        <v>41</v>
-      </c>
-      <c r="T22" t="s">
-        <v>42</v>
-      </c>
-      <c r="U22" t="s">
-        <v>37</v>
-      </c>
-      <c r="V22" t="s">
-        <v>235</v>
-      </c>
-      <c r="W22" t="s">
-        <v>233</v>
-      </c>
-      <c r="X22" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>243</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" t="s">
+        <v>239</v>
+      </c>
+      <c r="I23" t="s">
+        <v>240</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>241</v>
+      </c>
+      <c r="L23" t="s">
+        <v>242</v>
+      </c>
+      <c r="M23" t="s">
+        <v>76</v>
+      </c>
+      <c r="N23" t="s">
+        <v>36</v>
+      </c>
+      <c r="O23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q23" t="s">
         <v>244</v>
       </c>
-      <c r="D23" t="s">
+      <c r="R23" t="s">
+        <v>39</v>
+      </c>
+      <c r="S23" t="s">
+        <v>40</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" t="s">
+        <v>238</v>
+      </c>
+      <c r="W23" t="s">
+        <v>236</v>
+      </c>
+      <c r="X23" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y23" t="s">
         <v>245</v>
       </c>
-      <c r="E23" t="s">
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>246</v>
       </c>
-      <c r="F23" t="s">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>247</v>
+      </c>
+      <c r="D24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" t="s">
+        <v>247</v>
+      </c>
+      <c r="H24" t="s">
+        <v>250</v>
+      </c>
+      <c r="I24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" t="s">
+        <v>252</v>
+      </c>
+      <c r="M24" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" t="s">
+        <v>36</v>
+      </c>
+      <c r="O24" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>254</v>
+      </c>
+      <c r="R24" t="s">
+        <v>39</v>
+      </c>
+      <c r="S24" t="s">
+        <v>40</v>
+      </c>
+      <c r="T24" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" t="s">
+        <v>249</v>
+      </c>
+      <c r="W24" t="s">
+        <v>247</v>
+      </c>
+      <c r="X24" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" t="s">
+        <v>259</v>
+      </c>
+      <c r="F25" t="s">
+        <v>257</v>
+      </c>
+      <c r="G25" t="s">
+        <v>260</v>
+      </c>
+      <c r="H25" t="s">
+        <v>261</v>
+      </c>
+      <c r="I25" t="s">
+        <v>262</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>197</v>
+      </c>
+      <c r="L25" t="s">
+        <v>208</v>
+      </c>
+      <c r="M25" t="s">
+        <v>35</v>
+      </c>
+      <c r="N25" t="s">
+        <v>36</v>
+      </c>
+      <c r="O25" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" t="s">
         <v>37</v>
       </c>
-      <c r="G23" t="s">
-        <v>244</v>
-      </c>
-      <c r="H23" t="s">
-        <v>247</v>
-      </c>
-      <c r="I23" t="s">
-        <v>248</v>
-      </c>
-      <c r="J23" t="s">
-        <v>33</v>
-      </c>
-      <c r="K23" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" t="s">
-        <v>249</v>
-      </c>
-      <c r="M23" t="s">
-        <v>54</v>
-      </c>
-      <c r="N23" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" t="s">
-        <v>37</v>
-      </c>
-      <c r="P23" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>251</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="Q25" t="s">
+        <v>263</v>
+      </c>
+      <c r="R25" t="s">
+        <v>39</v>
+      </c>
+      <c r="S25" t="s">
         <v>40</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T25" t="s">
         <v>41</v>
       </c>
-      <c r="T23" t="s">
-        <v>42</v>
-      </c>
-      <c r="U23" t="s">
-        <v>37</v>
-      </c>
-      <c r="V23" t="s">
-        <v>246</v>
-      </c>
-      <c r="W23" t="s">
-        <v>244</v>
-      </c>
-      <c r="X23" t="s">
-        <v>244</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>37</v>
+      <c r="U25" t="s">
+        <v>36</v>
+      </c>
+      <c r="V25" t="s">
+        <v>259</v>
+      </c>
+      <c r="W25" t="s">
+        <v>260</v>
+      </c>
+      <c r="X25" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>254</v>
-      </c>
-      <c r="D24" t="s">
-        <v>255</v>
-      </c>
-      <c r="E24" t="s">
-        <v>256</v>
-      </c>
-      <c r="F24" t="s">
-        <v>254</v>
-      </c>
-      <c r="G24" t="s">
-        <v>257</v>
-      </c>
-      <c r="H24" t="s">
-        <v>258</v>
-      </c>
-      <c r="I24" t="s">
-        <v>259</v>
-      </c>
-      <c r="J24" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" t="s">
-        <v>198</v>
-      </c>
-      <c r="L24" t="s">
-        <v>209</v>
-      </c>
-      <c r="M24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N24" t="s">
-        <v>37</v>
-      </c>
-      <c r="O24" t="s">
-        <v>37</v>
-      </c>
-      <c r="P24" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>260</v>
-      </c>
-      <c r="R24" t="s">
-        <v>40</v>
-      </c>
-      <c r="S24" t="s">
-        <v>41</v>
-      </c>
-      <c r="T24" t="s">
-        <v>42</v>
-      </c>
-      <c r="U24" t="s">
-        <v>37</v>
-      </c>
-      <c r="V24" t="s">
-        <v>256</v>
-      </c>
-      <c r="W24" t="s">
-        <v>257</v>
-      </c>
-      <c r="X24" t="s">
-        <v>254</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>37</v>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>